--- a/data/trans_orig/IP04D$notiene-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$notiene-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>8767</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82039</t>
+          <t>82104</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88723</t>
+          <t>88827</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86181</t>
+          <t>86179</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>170726</t>
+          <t>170930</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>178097</t>
+          <t>177996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88141</t>
+          <t>88172</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88997</t>
+          <t>88432</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95527</t>
+          <t>95393</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>179692</t>
+          <t>179409</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187229</t>
+          <t>187194</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>858</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>7608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11446</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79210</t>
+          <t>79768</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84980</t>
+          <t>85011</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79591</t>
+          <t>79282</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86030</t>
+          <t>86032</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161601</t>
+          <t>161359</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>170207</t>
+          <t>170012</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11712</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>19459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26923</t>
+          <t>27392</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>194396</t>
+          <t>194580</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203314</t>
+          <t>202878</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>208529</t>
+          <t>208019</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>220760</t>
+          <t>219653</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>406662</t>
+          <t>406193</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>421594</t>
+          <t>421101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>15686</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23639</t>
+          <t>23292</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131583</t>
+          <t>131868</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>141894</t>
+          <t>142178</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129055</t>
+          <t>129284</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137561</t>
+          <t>137496</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>264319</t>
+          <t>264666</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>277442</t>
+          <t>278251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7876</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45879</t>
+          <t>46743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71551</t>
+          <t>70947</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>119380</t>
+          <t>119130</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126641</t>
+          <t>126649</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19021</t>
+          <t>18811</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35772</t>
+          <t>36281</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19203</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36954</t>
+          <t>36274</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41610</t>
+          <t>41958</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66286</t>
+          <t>65636</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>639673</t>
+          <t>639164</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>656424</t>
+          <t>656634</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>678397</t>
+          <t>679077</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>696148</t>
+          <t>695682</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1324510</t>
+          <t>1325160</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1349186</t>
+          <t>1348838</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>11591</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16019</t>
+          <t>16391</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>11191</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24033</t>
+          <t>24468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71393</t>
+          <t>71499</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79645</t>
+          <t>79428</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83019</t>
+          <t>82647</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92740</t>
+          <t>92945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158095</t>
+          <t>157660</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>170470</t>
+          <t>170937</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16157</t>
+          <t>15512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>12002</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24032</t>
+          <t>25228</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91459</t>
+          <t>90719</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100409</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95919</t>
+          <t>96564</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106421</t>
+          <t>106609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>192465</t>
+          <t>191269</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>205274</t>
+          <t>204495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>15434</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>7764</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20507</t>
+          <t>20445</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52852</t>
+          <t>53181</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59931</t>
+          <t>60214</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59895</t>
+          <t>59348</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69619</t>
+          <t>69683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116115</t>
+          <t>116177</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128584</t>
+          <t>128858</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26961</t>
+          <t>26826</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45531</t>
+          <t>43974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25737</t>
+          <t>25131</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42524</t>
+          <t>43750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57514</t>
+          <t>57544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82100</t>
+          <t>84286</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178046</t>
+          <t>179603</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196616</t>
+          <t>196751</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>166238</t>
+          <t>165012</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183025</t>
+          <t>183631</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>350239</t>
+          <t>348053</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>374825</t>
+          <t>374795</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,69%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14897</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27757</t>
+          <t>27545</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18461</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33501</t>
+          <t>34241</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36982</t>
+          <t>35961</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55879</t>
+          <t>55397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107774</t>
+          <t>107986</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>120634</t>
+          <t>121433</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108922</t>
+          <t>108182</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123962</t>
+          <t>123814</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>222075</t>
+          <t>222557</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>240972</t>
+          <t>241993</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,06%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17283</t>
+          <t>16512</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20880</t>
+          <t>20906</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19379</t>
+          <t>18877</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34139</t>
+          <t>33773</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43804</t>
+          <t>44575</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54036</t>
+          <t>54227</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46945</t>
+          <t>46919</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58719</t>
+          <t>58511</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94773</t>
+          <t>95139</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109533</t>
+          <t>110035</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,36%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72291</t>
+          <t>73572</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99409</t>
+          <t>100484</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>87144</t>
+          <t>86351</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118822</t>
+          <t>117902</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169589</t>
+          <t>168896</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>210215</t>
+          <t>208998</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>570137</t>
+          <t>569062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>597255</t>
+          <t>595974</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>586082</t>
+          <t>587002</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>617760</t>
+          <t>618553</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1164236</t>
+          <t>1165453</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1204862</t>
+          <t>1205555</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,71%</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13613</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>43403</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49211</t>
+          <t>49687</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99976</t>
+          <t>100043</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96720</t>
+          <t>91855</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121645</t>
+          <t>121781</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>190508</t>
+          <t>190032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>219415</t>
+          <t>219680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19941</t>
+          <t>19292</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>17464</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16409</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33227</t>
+          <t>33708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74740</t>
+          <t>75389</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86192</t>
+          <t>86263</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78077</t>
+          <t>78109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89861</t>
+          <t>90044</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>157027</t>
+          <t>156546</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173845</t>
+          <t>173309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15745</t>
+          <t>16145</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16705</t>
+          <t>16407</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12491</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26986</t>
+          <t>27840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36116</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45726</t>
+          <t>45523</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47148</t>
+          <t>47446</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59626</t>
+          <t>59296</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88728</t>
+          <t>87874</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103223</t>
+          <t>103013</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,02%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19846</t>
+          <t>19092</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53165</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18679</t>
+          <t>18048</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36790</t>
+          <t>36678</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43541</t>
+          <t>42974</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80834</t>
+          <t>79973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164661</t>
+          <t>167799</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197980</t>
+          <t>198734</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>181482</t>
+          <t>181594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>199593</t>
+          <t>200224</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>355263</t>
+          <t>356124</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>392556</t>
+          <t>393123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,15%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12937</t>
+          <t>12940</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26804</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16733</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36149</t>
+          <t>35824</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33623</t>
+          <t>33476</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57041</t>
+          <t>56396</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92624</t>
+          <t>93443</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106491</t>
+          <t>106488</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126468</t>
+          <t>126793</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145884</t>
+          <t>145970</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225004</t>
+          <t>225649</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>248422</t>
+          <t>248569</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>13579</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15540</t>
+          <t>15792</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8685</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24165</t>
+          <t>23664</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56976</t>
+          <t>55316</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66578</t>
+          <t>66303</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56463</t>
+          <t>56211</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67592</t>
+          <t>67479</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116733</t>
+          <t>117234</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>132213</t>
+          <t>132307</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72615</t>
+          <t>72427</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>112835</t>
+          <t>112454</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83856</t>
+          <t>81579</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>125885</t>
+          <t>123317</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>164388</t>
+          <t>166358</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>223602</t>
+          <t>223191</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>544318</t>
+          <t>544699</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>584538</t>
+          <t>584726</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>621690</t>
+          <t>624258</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>663719</t>
+          <t>665996</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1181126</t>
+          <t>1181537</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1240340</t>
+          <t>1238370</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$notiene-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$notiene-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3441</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7829</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1277</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7511</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3584</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8767</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89138</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>86554</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,42%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>86492</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>82104</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>88827</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>82422</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>88656</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,17%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>89138</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>86179</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>170930</t>
+          <t>170378</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177996</t>
+          <t>178132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>89933</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>89933</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>89933</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3508</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7432</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1367</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4303</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4734</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,48%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3508</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1385</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8346</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>93270</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>89346</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>95535</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,32%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>91108</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>88172</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>87741</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>92475</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,52%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,88%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>93270</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>88432</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>95393</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>91,38%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>268</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>179409</t>
+          <t>179002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187194</t>
+          <t>187028</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92475</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92475</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92475</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3248</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7816</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3090</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1146</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6389</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6951</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,59%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3248</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7608</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -1526,67 +1526,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>83642</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>79074</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>86029</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>83067</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>79768</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>85011</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>79206</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>85027</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,41%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,58%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>83642</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>79282</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>86032</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,26%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161359</t>
+          <t>160941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>170012</t>
+          <t>170052</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12438</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7343</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19500</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6299</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3230</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11528</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3055</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11693</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,06%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12438</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7825</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19459</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12296</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27392</t>
+          <t>26712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>215040</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>207978</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>220135</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,53%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,43%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>290</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>199809</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>194580</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>202878</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>194415</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>203053</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,94%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>215040</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>208019</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>219653</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,53%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>406193</t>
+          <t>406873</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>421101</t>
+          <t>421289</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>227478</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>227478</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>227478</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>299</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206108</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206108</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206108</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>227478</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>227478</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>227478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6248</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3027</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11050</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>9777</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5376</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15686</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5379</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>16047</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>6,63%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6248</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2907</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11119</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9707</t>
+          <t>10379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23292</t>
+          <t>23852</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>134155</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>129353</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>137376</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,84%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>197</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>137777</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>131868</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>142178</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>131507</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>142175</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>93,37%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,37%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>134155</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>129284</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>137496</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,55%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>264666</t>
+          <t>264106</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278251</t>
+          <t>277579</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>140403</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>140403</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>140403</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>147554</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>147554</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>147554</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>140403</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>140403</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>140403</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,92 +2437,92 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3383</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,57%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2033</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6474</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6861</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>3,82%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>12,89%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>607</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3091</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2640</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8126</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -2550,74 +2550,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>73431</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>70655</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>95,43%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>51184</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>46743</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>46356</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>53217</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>96,18%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>87,84%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>87,11%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>73431</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>70947</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>95,82%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>179</t>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>119130</t>
+          <t>119900</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53217</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53217</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53217</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>26674</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>19061</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>37183</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>26007</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>18811</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>36281</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>18356</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>35590</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>3,85%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>26674</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>19669</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>36274</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41958</t>
+          <t>41186</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65636</t>
+          <t>64975</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>688677</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>678168</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>696290</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>96,27%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>94,8%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>649438</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>639164</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>656634</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>639855</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>657089</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>96,15%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>94,63%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>688677</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>679077</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>695682</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1325160</t>
+          <t>1325821</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1348838</t>
+          <t>1349610</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>715351</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>715351</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>715351</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>976</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>675445</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>675445</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>675445</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1021</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>715351</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>715351</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>715351</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,72 +3357,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10240</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15966</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,34%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6677</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3662</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11591</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3612</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12179</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,04%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10240</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6093</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>16391</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11191</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24468</t>
+          <t>23589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -3470,72 +3470,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>88798</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>83072</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>93038</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,66%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,88%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,94%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>76413</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>71499</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>79428</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>70911</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>79478</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,96%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,59%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>88798</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>82647</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>92945</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157660</t>
+          <t>158539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>170937</t>
+          <t>170449</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99038</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99038</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99038</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99038</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99038</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,72 +3700,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9828</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5536</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15179</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7758</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4415</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13702</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13165</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,43%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9828</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5467</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15512</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12002</t>
+          <t>11460</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25228</t>
+          <t>24523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -3813,72 +3813,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>102248</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>96897</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>106540</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,46%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,06%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>96663</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>90719</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>100006</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>91256</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>100217</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,57%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,77%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>102248</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>96564</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>106609</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191269</t>
+          <t>191974</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204495</t>
+          <t>205037</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112076</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112076</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112076</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104421</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104421</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104421</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112076</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112076</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112076</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4043,72 +4043,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5037</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14851</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,74%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4246</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1626</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8659</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8899</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,87%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9206</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5099</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15434</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,31%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20445</t>
+          <t>20510</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -4156,72 +4156,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>65576</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>59931</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>69745</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,14%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,26%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>57594</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53181</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>60214</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>52941</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>60221</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,13%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,37%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>65576</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>59348</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>69683</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>87,69%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116177</t>
+          <t>116112</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128858</t>
+          <t>128254</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>74782</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>74782</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>74782</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>74782</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>74782</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>74782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,72 +4386,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33515</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24962</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>43293</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,05%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,96%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>26826</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>43974</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>27350</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>44100</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,7%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>33515</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>25131</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>43750</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57544</t>
+          <t>56745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84286</t>
+          <t>81565</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -4499,72 +4499,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>175247</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>165469</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>183800</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,95%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>79,26%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,04%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>188476</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>179603</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>196751</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>179477</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>196227</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,3%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>175247</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>165012</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>183631</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>83,95%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>348053</t>
+          <t>350774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>374795</t>
+          <t>375594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>208762</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208762</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208762</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>208762</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>208762</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>208762</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25136</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18070</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>32960</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>17,65%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>23,14%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>20613</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14098</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>27545</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14400</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>28022</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>15,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,4%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>25136</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18609</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>34241</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>17,65%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35961</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55397</t>
+          <t>56599</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -4842,72 +4842,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>117287</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>109463</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>124353</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>82,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>76,86%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,31%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>114918</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>107986</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>121433</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>107509</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>121131</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>84,79%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,68%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>89,6%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>117287</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>108182</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>123814</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>82,35%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>222557</t>
+          <t>221355</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241993</t>
+          <t>240850</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>142423</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>142423</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>142423</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>135531</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>135531</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>135531</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>142423</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>142423</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>142423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14672</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9696</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>21153</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>21,63%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>31,19%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>11399</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>6860</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>16512</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>7151</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>17125</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>18,66%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>14672</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>9314</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>20906</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>21,63%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>19582</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33773</t>
+          <t>33734</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -5185,72 +5185,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>53153</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>46672</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>58129</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>78,37%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>68,81%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>85,7%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>49688</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>44575</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>54227</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>43962</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>53936</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>81,34%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>72,97%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>88,77%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>53153</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>46919</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>58511</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>78,37%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95139</t>
+          <t>95178</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110035</t>
+          <t>109330</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>84,81%</t>
         </is>
       </c>
     </row>
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>102596</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>88182</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>119994</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>17,02%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>85794</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>73572</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>100484</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>72842</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>100512</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>12,81%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>10,99%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>15,01%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>102596</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>86351</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>117902</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>14,55%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>12,25%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>16,73%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>275</t>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>168896</t>
+          <t>168100</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>208998</t>
+          <t>210011</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -5528,72 +5528,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>602308</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>584910</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>616722</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>85,45%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>82,98%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>87,49%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>878</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>583752</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>569062</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>595974</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>569034</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>596704</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>87,19%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>84,99%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>89,01%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>602308</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>587002</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>618553</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>85,45%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>83,27%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1165453</t>
+          <t>1164440</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1205555</t>
+          <t>1206351</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -5646,52 +5646,52 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>704904</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>704904</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>704904</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>669546</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>669546</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>669546</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>704904</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>704904</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>704904</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,72 +5992,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14071</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8580</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22090</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8289</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4419</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14065</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22983</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13477</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43403</t>
+          <t>14178</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>31272</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20039</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49687</t>
+          <t>31088</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -6105,72 +6105,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>106930</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>98911</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>112421</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>81,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,91%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>96173</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>90397</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>100043</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>92,07%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,54%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,77%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>112275</t>
+          <t>94933</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91855</t>
+          <t>88749</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121781</t>
+          <t>98352</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>208447</t>
+          <t>201863</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>190032</t>
+          <t>192840</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>219680</t>
+          <t>208649</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121001</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121001</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121001</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135258</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135258</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135258</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>239719</t>
+          <t>223928</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>239719</t>
+          <t>223928</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>239719</t>
+          <t>223928</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6335,72 +6335,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10160</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5551</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16939</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,12%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13222</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8418</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19292</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13,96%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,89%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,38%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>13536</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>23696</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16945</t>
+          <t>16178</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33708</t>
+          <t>33406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -6448,72 +6448,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>81238</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>74459</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>85847</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,88%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>81459</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>75389</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>86263</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>86,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,62%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>85092</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78109</t>
+          <t>75991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90044</t>
+          <t>88159</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>166551</t>
+          <t>164248</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>156546</t>
+          <t>154538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173309</t>
+          <t>171766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6678,72 +6678,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6382</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3011</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11168</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10280</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6338</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16145</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>15478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27840</t>
+          <t>23840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -6791,72 +6791,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>50559</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>45773</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>53930</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,39%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,71%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>41581</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>35716</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>45523</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>80,18%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>68,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,78%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>55222</t>
+          <t>43316</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47446</t>
+          <t>38004</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59296</t>
+          <t>47611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>96803</t>
+          <t>93874</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87874</t>
+          <t>86583</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103013</t>
+          <t>99349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24454</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16697</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33275</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>32712</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19092</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>50027</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15,02%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26359</t>
+          <t>22009</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18048</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36678</t>
+          <t>30360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>59071</t>
+          <t>46463</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42974</t>
+          <t>35957</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79973</t>
+          <t>56664</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>177490</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>168669</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>185247</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,89%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,73%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>185114</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>167799</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>198734</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>84,98%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>191913</t>
+          <t>156574</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>181594</t>
+          <t>148223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200224</t>
+          <t>163248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>377026</t>
+          <t>334065</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>356124</t>
+          <t>323864</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>393123</t>
+          <t>344571</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7364,72 +7364,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>21061</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13730</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>28831</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>14,21%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19,45%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>18663</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12940</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25985</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15,63%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,83%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25034</t>
+          <t>18076</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16647</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35824</t>
+          <t>26026</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>43697</t>
+          <t>39137</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33476</t>
+          <t>29585</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56396</t>
+          <t>49422</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -7477,72 +7477,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>127182</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>119412</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>134513</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>85,79%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>80,55%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,74%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>100765</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>93443</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>106488</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>84,37%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>78,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>89,17%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>137583</t>
+          <t>100655</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126793</t>
+          <t>92705</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145970</t>
+          <t>106529</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>238348</t>
+          <t>227837</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225649</t>
+          <t>217552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>248569</t>
+          <t>237389</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7707,72 +7707,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8222</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4199</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>15599</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>12,04%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>22,84%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>6009</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2592</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>13579</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>19,71%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8635</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23664</t>
+          <t>19839</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -7820,72 +7820,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>60065</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>52688</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>64088</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>87,96%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>77,16%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>93,85%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>62886</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>55316</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>66303</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>91,28%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>80,29%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>63368</t>
+          <t>65973</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56211</t>
+          <t>62133</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67479</t>
+          <t>68611</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>126254</t>
+          <t>126040</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117234</t>
+          <t>118805</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>132307</t>
+          <t>131332</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>89175</t>
+          <t>84349</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72427</t>
+          <t>68298</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>112454</t>
+          <t>100784</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8090,32 +8090,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>102123</t>
+          <t>76164</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>81579</t>
+          <t>63892</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>123317</t>
+          <t>90549</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>191298</t>
+          <t>160513</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>166358</t>
+          <t>140977</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>223191</t>
+          <t>184591</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>603465</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>587030</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>619516</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>87,74%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>85,35%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>90,07%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>813</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>567978</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>544699</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>584726</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>86,43%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>82,89%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>88,98%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>841</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>645452</t>
+          <t>544463</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>624258</t>
+          <t>530078</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>665996</t>
+          <t>556735</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1213430</t>
+          <t>1147928</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1181537</t>
+          <t>1123850</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1238370</t>
+          <t>1167464</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>687814</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>687814</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>687814</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>747575</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>747575</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>747575</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1404728</t>
+          <t>1308441</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1404728</t>
+          <t>1308441</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1404728</t>
+          <t>1308441</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
